--- a/excels/2급_분개문제(AI).xlsx
+++ b/excels/2급_분개문제(AI).xlsx
@@ -35248,9 +35248,9 @@
       </c>
       <c r="E592" t="inlineStr">
         <is>
-          <t>3
-1
-500</t>
+          <t>3,000,000
+1,500,000
+500,000</t>
         </is>
       </c>
       <c r="G592" t="inlineStr">
@@ -35260,7 +35260,7 @@
       </c>
       <c r="H592" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="I592" t="inlineStr">
@@ -35280,7 +35280,7 @@
       </c>
       <c r="E593" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>600,000</t>
         </is>
       </c>
       <c r="G593" t="inlineStr">
@@ -35291,8 +35291,8 @@
       </c>
       <c r="H593" t="inlineStr">
         <is>
-          <t>500
-100</t>
+          <t>500,000
+100,000</t>
         </is>
       </c>
       <c r="I593" t="inlineStr">
@@ -35312,7 +35312,7 @@
       </c>
       <c r="E594" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1,200,000</t>
         </is>
       </c>
       <c r="G594" t="inlineStr">
@@ -35323,8 +35323,8 @@
       </c>
       <c r="H594" t="inlineStr">
         <is>
-          <t>1
-200</t>
+          <t>1,000,000
+200,000</t>
         </is>
       </c>
       <c r="I594" t="inlineStr">
@@ -35346,9 +35346,9 @@
       </c>
       <c r="E595" t="inlineStr">
         <is>
-          <t>3
-1
-500</t>
+          <t>3,000,000
+1,500,000
+500,000</t>
         </is>
       </c>
       <c r="G595" t="inlineStr">
@@ -35358,7 +35358,7 @@
       </c>
       <c r="H595" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="I595" t="inlineStr">
@@ -35378,7 +35378,7 @@
       </c>
       <c r="E596" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="G596" t="inlineStr">
@@ -35388,7 +35388,7 @@
       </c>
       <c r="H596" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="I596" t="inlineStr">
@@ -35408,7 +35408,7 @@
       </c>
       <c r="E597" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>600,000</t>
         </is>
       </c>
       <c r="G597" t="inlineStr">
@@ -35419,8 +35419,8 @@
       </c>
       <c r="H597" t="inlineStr">
         <is>
-          <t>500
-100</t>
+          <t>500,000
+100,000</t>
         </is>
       </c>
       <c r="I597" t="inlineStr">
@@ -35440,7 +35440,7 @@
       </c>
       <c r="E598" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>600,000</t>
         </is>
       </c>
       <c r="G598" t="inlineStr">
@@ -35451,8 +35451,8 @@
       </c>
       <c r="H598" t="inlineStr">
         <is>
-          <t>500
-100</t>
+          <t>500,000
+100,000</t>
         </is>
       </c>
       <c r="I598" t="inlineStr">
@@ -35472,7 +35472,7 @@
       </c>
       <c r="E599" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>600,000</t>
         </is>
       </c>
       <c r="G599" t="inlineStr">
@@ -35483,8 +35483,8 @@
       </c>
       <c r="H599" t="inlineStr">
         <is>
-          <t>500
-100</t>
+          <t>500,000
+100,000</t>
         </is>
       </c>
       <c r="I599" t="inlineStr">
@@ -35504,7 +35504,7 @@
       </c>
       <c r="E600" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>600,000</t>
         </is>
       </c>
       <c r="G600" t="inlineStr">
@@ -35515,8 +35515,8 @@
       </c>
       <c r="H600" t="inlineStr">
         <is>
-          <t>500
-100</t>
+          <t>500,000
+100,000</t>
         </is>
       </c>
       <c r="I600" t="inlineStr">
@@ -35536,7 +35536,7 @@
       </c>
       <c r="E601" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1,200,000</t>
         </is>
       </c>
       <c r="G601" t="inlineStr">
@@ -35547,8 +35547,8 @@
       </c>
       <c r="H601" t="inlineStr">
         <is>
-          <t>1
-200</t>
+          <t>1,000,000
+200,000</t>
         </is>
       </c>
       <c r="I601" t="inlineStr">
@@ -35570,9 +35570,9 @@
       </c>
       <c r="E602" t="inlineStr">
         <is>
-          <t>3
-1
-500</t>
+          <t>3,000,000
+1,500,000
+500,000</t>
         </is>
       </c>
       <c r="G602" t="inlineStr">
@@ -35582,7 +35582,7 @@
       </c>
       <c r="H602" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="I602" t="inlineStr">
@@ -35604,9 +35604,9 @@
       </c>
       <c r="E603" t="inlineStr">
         <is>
-          <t>3
-1
-500</t>
+          <t>3,000,000
+1,500,000
+500,000</t>
         </is>
       </c>
       <c r="G603" t="inlineStr">
@@ -35616,7 +35616,7 @@
       </c>
       <c r="H603" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="I603" t="inlineStr">
@@ -35636,7 +35636,7 @@
       </c>
       <c r="E604" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="G604" t="inlineStr">
@@ -35646,7 +35646,7 @@
       </c>
       <c r="H604" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="I604" t="inlineStr">
@@ -35666,7 +35666,7 @@
       </c>
       <c r="E605" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1,200,000</t>
         </is>
       </c>
       <c r="G605" t="inlineStr">
@@ -35677,8 +35677,8 @@
       </c>
       <c r="H605" t="inlineStr">
         <is>
-          <t>1
-200</t>
+          <t>1,000,000
+200,000</t>
         </is>
       </c>
       <c r="I605" t="inlineStr">
@@ -35698,7 +35698,7 @@
       </c>
       <c r="E606" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="G606" t="inlineStr">
@@ -35708,7 +35708,7 @@
       </c>
       <c r="H606" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="I606" t="inlineStr">
@@ -35728,7 +35728,7 @@
       </c>
       <c r="E607" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1,200,000</t>
         </is>
       </c>
       <c r="G607" t="inlineStr">
@@ -35739,8 +35739,8 @@
       </c>
       <c r="H607" t="inlineStr">
         <is>
-          <t>1
-200</t>
+          <t>1,000,000
+200,000</t>
         </is>
       </c>
       <c r="I607" t="inlineStr">
@@ -35762,9 +35762,9 @@
       </c>
       <c r="E608" t="inlineStr">
         <is>
-          <t>3
-1
-500</t>
+          <t>3,000,000
+1,500,000
+500,000</t>
         </is>
       </c>
       <c r="G608" t="inlineStr">
@@ -35774,7 +35774,7 @@
       </c>
       <c r="H608" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="I608" t="inlineStr">
@@ -35796,9 +35796,9 @@
       </c>
       <c r="E609" t="inlineStr">
         <is>
-          <t>3
-1
-500</t>
+          <t>3,000,000
+1,500,000
+500,000</t>
         </is>
       </c>
       <c r="G609" t="inlineStr">
@@ -35808,7 +35808,7 @@
       </c>
       <c r="H609" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="I609" t="inlineStr">
@@ -35828,7 +35828,7 @@
       </c>
       <c r="E610" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>600,000</t>
         </is>
       </c>
       <c r="G610" t="inlineStr">
@@ -35839,8 +35839,8 @@
       </c>
       <c r="H610" t="inlineStr">
         <is>
-          <t>500
-100</t>
+          <t>500,000
+100,000</t>
         </is>
       </c>
       <c r="I610" t="inlineStr">
@@ -35860,7 +35860,7 @@
       </c>
       <c r="E611" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1,200,000</t>
         </is>
       </c>
       <c r="G611" t="inlineStr">
@@ -35871,8 +35871,8 @@
       </c>
       <c r="H611" t="inlineStr">
         <is>
-          <t>1
-200</t>
+          <t>1,000,000
+200,000</t>
         </is>
       </c>
       <c r="I611" t="inlineStr">
@@ -35892,7 +35892,7 @@
       </c>
       <c r="E612" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1,200,000</t>
         </is>
       </c>
       <c r="G612" t="inlineStr">
@@ -35903,8 +35903,8 @@
       </c>
       <c r="H612" t="inlineStr">
         <is>
-          <t>1
-200</t>
+          <t>1,000,000
+200,000</t>
         </is>
       </c>
       <c r="I612" t="inlineStr">
@@ -35926,9 +35926,9 @@
       </c>
       <c r="E613" t="inlineStr">
         <is>
-          <t>3
-1
-500</t>
+          <t>3,000,000
+1,500,000
+500,000</t>
         </is>
       </c>
       <c r="G613" t="inlineStr">
@@ -35938,7 +35938,7 @@
       </c>
       <c r="H613" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="I613" t="inlineStr">
@@ -35960,9 +35960,9 @@
       </c>
       <c r="E614" t="inlineStr">
         <is>
-          <t>3
-1
-500</t>
+          <t>3,000,000
+1,500,000
+500,000</t>
         </is>
       </c>
       <c r="G614" t="inlineStr">
@@ -35972,7 +35972,7 @@
       </c>
       <c r="H614" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="I614" t="inlineStr">
@@ -35992,7 +35992,7 @@
       </c>
       <c r="E615" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1,200,000</t>
         </is>
       </c>
       <c r="G615" t="inlineStr">
@@ -36003,8 +36003,8 @@
       </c>
       <c r="H615" t="inlineStr">
         <is>
-          <t>1
-200</t>
+          <t>1,000,000
+200,000</t>
         </is>
       </c>
       <c r="I615" t="inlineStr">
@@ -36024,7 +36024,7 @@
       </c>
       <c r="E616" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="G616" t="inlineStr">
@@ -36034,7 +36034,7 @@
       </c>
       <c r="H616" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="I616" t="inlineStr">
@@ -36054,7 +36054,7 @@
       </c>
       <c r="E617" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1,200,000</t>
         </is>
       </c>
       <c r="G617" t="inlineStr">
@@ -36065,8 +36065,8 @@
       </c>
       <c r="H617" t="inlineStr">
         <is>
-          <t>1
-200</t>
+          <t>1,000,000
+200,000</t>
         </is>
       </c>
       <c r="I617" t="inlineStr">
@@ -36088,9 +36088,9 @@
       </c>
       <c r="E618" t="inlineStr">
         <is>
-          <t>3
-1
-500</t>
+          <t>3,000,000
+1,500,000
+500,000</t>
         </is>
       </c>
       <c r="G618" t="inlineStr">
@@ -36100,7 +36100,7 @@
       </c>
       <c r="H618" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="I618" t="inlineStr">
@@ -36120,7 +36120,7 @@
       </c>
       <c r="E619" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="G619" t="inlineStr">
@@ -36130,7 +36130,7 @@
       </c>
       <c r="H619" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="I619" t="inlineStr">
@@ -36152,9 +36152,9 @@
       </c>
       <c r="E620" t="inlineStr">
         <is>
-          <t>3
-1
-500</t>
+          <t>3,000,000
+1,500,000
+500,000</t>
         </is>
       </c>
       <c r="G620" t="inlineStr">
@@ -36164,7 +36164,7 @@
       </c>
       <c r="H620" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="I620" t="inlineStr">
@@ -36186,9 +36186,9 @@
       </c>
       <c r="E621" t="inlineStr">
         <is>
-          <t>3
-1
-500</t>
+          <t>3,000,000
+1,500,000
+500,000</t>
         </is>
       </c>
       <c r="G621" t="inlineStr">
@@ -36198,7 +36198,7 @@
       </c>
       <c r="H621" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="I621" t="inlineStr">
@@ -36218,7 +36218,7 @@
       </c>
       <c r="E622" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1,200,000</t>
         </is>
       </c>
       <c r="G622" t="inlineStr">
@@ -36229,8 +36229,8 @@
       </c>
       <c r="H622" t="inlineStr">
         <is>
-          <t>1
-200</t>
+          <t>1,000,000
+200,000</t>
         </is>
       </c>
       <c r="I622" t="inlineStr">
@@ -36250,7 +36250,7 @@
       </c>
       <c r="E623" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="G623" t="inlineStr">
@@ -36260,7 +36260,7 @@
       </c>
       <c r="H623" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="I623" t="inlineStr">
@@ -36282,9 +36282,9 @@
       </c>
       <c r="E624" t="inlineStr">
         <is>
-          <t>3
-1
-500</t>
+          <t>3,000,000
+1,500,000
+500,000</t>
         </is>
       </c>
       <c r="G624" t="inlineStr">
@@ -36294,7 +36294,7 @@
       </c>
       <c r="H624" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="I624" t="inlineStr">
@@ -36314,7 +36314,7 @@
       </c>
       <c r="E625" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>600,000</t>
         </is>
       </c>
       <c r="G625" t="inlineStr">
@@ -36325,8 +36325,8 @@
       </c>
       <c r="H625" t="inlineStr">
         <is>
-          <t>500
-100</t>
+          <t>500,000
+100,000</t>
         </is>
       </c>
       <c r="I625" t="inlineStr">
@@ -36346,7 +36346,7 @@
       </c>
       <c r="E626" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="G626" t="inlineStr">
@@ -36356,7 +36356,7 @@
       </c>
       <c r="H626" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="I626" t="inlineStr">
@@ -36376,7 +36376,7 @@
       </c>
       <c r="E627" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1,200,000</t>
         </is>
       </c>
       <c r="G627" t="inlineStr">
@@ -36387,8 +36387,8 @@
       </c>
       <c r="H627" t="inlineStr">
         <is>
-          <t>1
-200</t>
+          <t>1,000,000
+200,000</t>
         </is>
       </c>
       <c r="I627" t="inlineStr">
@@ -36408,7 +36408,7 @@
       </c>
       <c r="E628" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1,200,000</t>
         </is>
       </c>
       <c r="G628" t="inlineStr">
@@ -36419,8 +36419,8 @@
       </c>
       <c r="H628" t="inlineStr">
         <is>
-          <t>1
-200</t>
+          <t>1,000,000
+200,000</t>
         </is>
       </c>
       <c r="I628" t="inlineStr">
@@ -36440,7 +36440,7 @@
       </c>
       <c r="E629" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>600,000</t>
         </is>
       </c>
       <c r="G629" t="inlineStr">
@@ -36451,8 +36451,8 @@
       </c>
       <c r="H629" t="inlineStr">
         <is>
-          <t>500
-100</t>
+          <t>500,000
+100,000</t>
         </is>
       </c>
       <c r="I629" t="inlineStr">
@@ -36472,7 +36472,7 @@
       </c>
       <c r="E630" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="G630" t="inlineStr">
@@ -36482,7 +36482,7 @@
       </c>
       <c r="H630" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="I630" t="inlineStr">
@@ -36502,7 +36502,7 @@
       </c>
       <c r="E631" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1,200,000</t>
         </is>
       </c>
       <c r="G631" t="inlineStr">
@@ -36513,8 +36513,8 @@
       </c>
       <c r="H631" t="inlineStr">
         <is>
-          <t>1
-200</t>
+          <t>1,000,000
+200,000</t>
         </is>
       </c>
       <c r="I631" t="inlineStr">
@@ -36534,7 +36534,7 @@
       </c>
       <c r="E632" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="G632" t="inlineStr">
@@ -36544,7 +36544,7 @@
       </c>
       <c r="H632" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="I632" t="inlineStr">
@@ -36564,7 +36564,7 @@
       </c>
       <c r="E633" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>600,000</t>
         </is>
       </c>
       <c r="G633" t="inlineStr">
@@ -36575,8 +36575,8 @@
       </c>
       <c r="H633" t="inlineStr">
         <is>
-          <t>500
-100</t>
+          <t>500,000
+100,000</t>
         </is>
       </c>
       <c r="I633" t="inlineStr">
@@ -36596,7 +36596,7 @@
       </c>
       <c r="E634" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="G634" t="inlineStr">
@@ -36606,7 +36606,7 @@
       </c>
       <c r="H634" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="I634" t="inlineStr">
@@ -36626,7 +36626,7 @@
       </c>
       <c r="E635" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1,200,000</t>
         </is>
       </c>
       <c r="G635" t="inlineStr">
@@ -36637,8 +36637,8 @@
       </c>
       <c r="H635" t="inlineStr">
         <is>
-          <t>1
-200</t>
+          <t>1,000,000
+200,000</t>
         </is>
       </c>
       <c r="I635" t="inlineStr">
@@ -36658,7 +36658,7 @@
       </c>
       <c r="E636" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1,200,000</t>
         </is>
       </c>
       <c r="G636" t="inlineStr">
@@ -36669,8 +36669,8 @@
       </c>
       <c r="H636" t="inlineStr">
         <is>
-          <t>1
-200</t>
+          <t>1,000,000
+200,000</t>
         </is>
       </c>
       <c r="I636" t="inlineStr">
@@ -36692,9 +36692,9 @@
       </c>
       <c r="E637" t="inlineStr">
         <is>
-          <t>3
-1
-500</t>
+          <t>3,000,000
+1,500,000
+500,000</t>
         </is>
       </c>
       <c r="G637" t="inlineStr">
@@ -36704,7 +36704,7 @@
       </c>
       <c r="H637" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="I637" t="inlineStr">
@@ -36724,7 +36724,7 @@
       </c>
       <c r="E638" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1,200,000</t>
         </is>
       </c>
       <c r="G638" t="inlineStr">
@@ -36735,8 +36735,8 @@
       </c>
       <c r="H638" t="inlineStr">
         <is>
-          <t>1
-200</t>
+          <t>1,000,000
+200,000</t>
         </is>
       </c>
       <c r="I638" t="inlineStr">
@@ -36758,9 +36758,9 @@
       </c>
       <c r="E639" t="inlineStr">
         <is>
-          <t>3
-1
-500</t>
+          <t>3,000,000
+1,500,000
+500,000</t>
         </is>
       </c>
       <c r="G639" t="inlineStr">
@@ -36770,7 +36770,7 @@
       </c>
       <c r="H639" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="I639" t="inlineStr">
@@ -36792,9 +36792,9 @@
       </c>
       <c r="E640" t="inlineStr">
         <is>
-          <t>3
-1
-500</t>
+          <t>3,000,000
+1,500,000
+500,000</t>
         </is>
       </c>
       <c r="G640" t="inlineStr">
@@ -36804,7 +36804,7 @@
       </c>
       <c r="H640" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="I640" t="inlineStr">
@@ -36826,9 +36826,9 @@
       </c>
       <c r="E641" t="inlineStr">
         <is>
-          <t>3
-1
-500</t>
+          <t>3,000,000
+1,500,000
+500,000</t>
         </is>
       </c>
       <c r="G641" t="inlineStr">
@@ -36838,7 +36838,7 @@
       </c>
       <c r="H641" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="I641" t="inlineStr">
@@ -36858,7 +36858,7 @@
       </c>
       <c r="E642" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1,200,000</t>
         </is>
       </c>
       <c r="G642" t="inlineStr">
@@ -36869,8 +36869,8 @@
       </c>
       <c r="H642" t="inlineStr">
         <is>
-          <t>1
-200</t>
+          <t>1,000,000
+200,000</t>
         </is>
       </c>
       <c r="I642" t="inlineStr">
@@ -36892,9 +36892,9 @@
       </c>
       <c r="E643" t="inlineStr">
         <is>
-          <t>3
-1
-500</t>
+          <t>3,000,000
+1,500,000
+500,000</t>
         </is>
       </c>
       <c r="G643" t="inlineStr">
@@ -36904,7 +36904,7 @@
       </c>
       <c r="H643" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="I643" t="inlineStr">
@@ -36924,7 +36924,7 @@
       </c>
       <c r="E644" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>600,000</t>
         </is>
       </c>
       <c r="G644" t="inlineStr">
@@ -36935,8 +36935,8 @@
       </c>
       <c r="H644" t="inlineStr">
         <is>
-          <t>500
-100</t>
+          <t>500,000
+100,000</t>
         </is>
       </c>
       <c r="I644" t="inlineStr">
@@ -36956,7 +36956,7 @@
       </c>
       <c r="E645" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="G645" t="inlineStr">
@@ -36966,7 +36966,7 @@
       </c>
       <c r="H645" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="I645" t="inlineStr">
@@ -36988,9 +36988,9 @@
       </c>
       <c r="E646" t="inlineStr">
         <is>
-          <t>3
-1
-500</t>
+          <t>3,000,000
+1,500,000
+500,000</t>
         </is>
       </c>
       <c r="G646" t="inlineStr">
@@ -37000,7 +37000,7 @@
       </c>
       <c r="H646" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="I646" t="inlineStr">
@@ -37020,7 +37020,7 @@
       </c>
       <c r="E647" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1,200,000</t>
         </is>
       </c>
       <c r="G647" t="inlineStr">
@@ -37031,8 +37031,8 @@
       </c>
       <c r="H647" t="inlineStr">
         <is>
-          <t>1
-200</t>
+          <t>1,000,000
+200,000</t>
         </is>
       </c>
       <c r="I647" t="inlineStr">
@@ -37052,7 +37052,7 @@
       </c>
       <c r="E648" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1,200,000</t>
         </is>
       </c>
       <c r="G648" t="inlineStr">
@@ -37063,8 +37063,8 @@
       </c>
       <c r="H648" t="inlineStr">
         <is>
-          <t>1
-200</t>
+          <t>1,000,000
+200,000</t>
         </is>
       </c>
       <c r="I648" t="inlineStr">
@@ -37086,9 +37086,9 @@
       </c>
       <c r="E649" t="inlineStr">
         <is>
-          <t>3
-1
-500</t>
+          <t>3,000,000
+1,500,000
+500,000</t>
         </is>
       </c>
       <c r="G649" t="inlineStr">
@@ -37098,7 +37098,7 @@
       </c>
       <c r="H649" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="I649" t="inlineStr">
@@ -37118,7 +37118,7 @@
       </c>
       <c r="E650" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>600,000</t>
         </is>
       </c>
       <c r="G650" t="inlineStr">
@@ -37129,8 +37129,8 @@
       </c>
       <c r="H650" t="inlineStr">
         <is>
-          <t>500
-100</t>
+          <t>500,000
+100,000</t>
         </is>
       </c>
       <c r="I650" t="inlineStr">
@@ -37150,7 +37150,7 @@
       </c>
       <c r="E651" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="G651" t="inlineStr">
@@ -37160,7 +37160,7 @@
       </c>
       <c r="H651" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="I651" t="inlineStr">
@@ -37180,7 +37180,7 @@
       </c>
       <c r="E652" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>600,000</t>
         </is>
       </c>
       <c r="G652" t="inlineStr">
@@ -37191,8 +37191,8 @@
       </c>
       <c r="H652" t="inlineStr">
         <is>
-          <t>500
-100</t>
+          <t>500,000
+100,000</t>
         </is>
       </c>
       <c r="I652" t="inlineStr">
@@ -37214,9 +37214,9 @@
       </c>
       <c r="E653" t="inlineStr">
         <is>
-          <t>3
-1
-500</t>
+          <t>3,000,000
+1,500,000
+500,000</t>
         </is>
       </c>
       <c r="G653" t="inlineStr">
@@ -37226,7 +37226,7 @@
       </c>
       <c r="H653" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="I653" t="inlineStr">
@@ -37246,7 +37246,7 @@
       </c>
       <c r="E654" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1,200,000</t>
         </is>
       </c>
       <c r="G654" t="inlineStr">
@@ -37257,8 +37257,8 @@
       </c>
       <c r="H654" t="inlineStr">
         <is>
-          <t>1
-200</t>
+          <t>1,000,000
+200,000</t>
         </is>
       </c>
       <c r="I654" t="inlineStr">
@@ -37278,7 +37278,7 @@
       </c>
       <c r="E655" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="G655" t="inlineStr">
@@ -37288,7 +37288,7 @@
       </c>
       <c r="H655" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="I655" t="inlineStr">
@@ -37308,7 +37308,7 @@
       </c>
       <c r="E656" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1,200,000</t>
         </is>
       </c>
       <c r="G656" t="inlineStr">
@@ -37319,8 +37319,8 @@
       </c>
       <c r="H656" t="inlineStr">
         <is>
-          <t>1
-200</t>
+          <t>1,000,000
+200,000</t>
         </is>
       </c>
       <c r="I656" t="inlineStr">
@@ -37342,9 +37342,9 @@
       </c>
       <c r="E657" t="inlineStr">
         <is>
-          <t>3
-1
-500</t>
+          <t>3,000,000
+1,500,000
+500,000</t>
         </is>
       </c>
       <c r="G657" t="inlineStr">
@@ -37354,7 +37354,7 @@
       </c>
       <c r="H657" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="I657" t="inlineStr">
@@ -37374,7 +37374,7 @@
       </c>
       <c r="E658" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="G658" t="inlineStr">
@@ -37384,7 +37384,7 @@
       </c>
       <c r="H658" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="I658" t="inlineStr">
@@ -37404,7 +37404,7 @@
       </c>
       <c r="E659" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="G659" t="inlineStr">
@@ -37414,7 +37414,7 @@
       </c>
       <c r="H659" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="I659" t="inlineStr">
@@ -37434,7 +37434,7 @@
       </c>
       <c r="E660" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="G660" t="inlineStr">
@@ -37444,7 +37444,7 @@
       </c>
       <c r="H660" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="I660" t="inlineStr">
@@ -37464,7 +37464,7 @@
       </c>
       <c r="E661" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>600,000</t>
         </is>
       </c>
       <c r="G661" t="inlineStr">
@@ -37475,8 +37475,8 @@
       </c>
       <c r="H661" t="inlineStr">
         <is>
-          <t>500
-100</t>
+          <t>500,000
+100,000</t>
         </is>
       </c>
       <c r="I661" t="inlineStr">
@@ -37496,7 +37496,7 @@
       </c>
       <c r="E662" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="G662" t="inlineStr">
@@ -37506,7 +37506,7 @@
       </c>
       <c r="H662" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="I662" t="inlineStr">
@@ -37528,9 +37528,9 @@
       </c>
       <c r="E663" t="inlineStr">
         <is>
-          <t>3
-1
-500</t>
+          <t>3,000,000
+1,500,000
+500,000</t>
         </is>
       </c>
       <c r="G663" t="inlineStr">
@@ -37540,7 +37540,7 @@
       </c>
       <c r="H663" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="I663" t="inlineStr">
@@ -37560,7 +37560,7 @@
       </c>
       <c r="E664" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>600,000</t>
         </is>
       </c>
       <c r="G664" t="inlineStr">
@@ -37571,8 +37571,8 @@
       </c>
       <c r="H664" t="inlineStr">
         <is>
-          <t>500
-100</t>
+          <t>500,000
+100,000</t>
         </is>
       </c>
       <c r="I664" t="inlineStr">
@@ -37592,7 +37592,7 @@
       </c>
       <c r="E665" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>600,000</t>
         </is>
       </c>
       <c r="G665" t="inlineStr">
@@ -37603,8 +37603,8 @@
       </c>
       <c r="H665" t="inlineStr">
         <is>
-          <t>500
-100</t>
+          <t>500,000
+100,000</t>
         </is>
       </c>
       <c r="I665" t="inlineStr">
@@ -37624,7 +37624,7 @@
       </c>
       <c r="E666" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="G666" t="inlineStr">
@@ -37634,7 +37634,7 @@
       </c>
       <c r="H666" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="I666" t="inlineStr">
@@ -37656,9 +37656,9 @@
       </c>
       <c r="E667" t="inlineStr">
         <is>
-          <t>3
-1
-500</t>
+          <t>3,000,000
+1,500,000
+500,000</t>
         </is>
       </c>
       <c r="G667" t="inlineStr">
@@ -37668,7 +37668,7 @@
       </c>
       <c r="H667" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="I667" t="inlineStr">
@@ -37688,7 +37688,7 @@
       </c>
       <c r="E668" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1,200,000</t>
         </is>
       </c>
       <c r="G668" t="inlineStr">
@@ -37699,8 +37699,8 @@
       </c>
       <c r="H668" t="inlineStr">
         <is>
-          <t>1
-200</t>
+          <t>1,000,000
+200,000</t>
         </is>
       </c>
       <c r="I668" t="inlineStr">
@@ -37720,7 +37720,7 @@
       </c>
       <c r="E669" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>600,000</t>
         </is>
       </c>
       <c r="G669" t="inlineStr">
@@ -37731,8 +37731,8 @@
       </c>
       <c r="H669" t="inlineStr">
         <is>
-          <t>500
-100</t>
+          <t>500,000
+100,000</t>
         </is>
       </c>
       <c r="I669" t="inlineStr">
@@ -37752,7 +37752,7 @@
       </c>
       <c r="E670" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1,200,000</t>
         </is>
       </c>
       <c r="G670" t="inlineStr">
@@ -37763,8 +37763,8 @@
       </c>
       <c r="H670" t="inlineStr">
         <is>
-          <t>1
-200</t>
+          <t>1,000,000
+200,000</t>
         </is>
       </c>
       <c r="I670" t="inlineStr">
@@ -37786,9 +37786,9 @@
       </c>
       <c r="E671" t="inlineStr">
         <is>
-          <t>3
-1
-500</t>
+          <t>3,000,000
+1,500,000
+500,000</t>
         </is>
       </c>
       <c r="G671" t="inlineStr">
@@ -37798,7 +37798,7 @@
       </c>
       <c r="H671" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="I671" t="inlineStr">
@@ -37818,7 +37818,7 @@
       </c>
       <c r="E672" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>600,000</t>
         </is>
       </c>
       <c r="G672" t="inlineStr">
@@ -37829,8 +37829,8 @@
       </c>
       <c r="H672" t="inlineStr">
         <is>
-          <t>500
-100</t>
+          <t>500,000
+100,000</t>
         </is>
       </c>
       <c r="I672" t="inlineStr">
@@ -37850,7 +37850,7 @@
       </c>
       <c r="E673" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="G673" t="inlineStr">
@@ -37860,7 +37860,7 @@
       </c>
       <c r="H673" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="I673" t="inlineStr">
@@ -37880,7 +37880,7 @@
       </c>
       <c r="E674" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="G674" t="inlineStr">
@@ -37890,7 +37890,7 @@
       </c>
       <c r="H674" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="I674" t="inlineStr">
@@ -37910,7 +37910,7 @@
       </c>
       <c r="E675" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="G675" t="inlineStr">
@@ -37920,7 +37920,7 @@
       </c>
       <c r="H675" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="I675" t="inlineStr">
@@ -37942,9 +37942,9 @@
       </c>
       <c r="E676" t="inlineStr">
         <is>
-          <t>3
-1
-500</t>
+          <t>3,000,000
+1,500,000
+500,000</t>
         </is>
       </c>
       <c r="G676" t="inlineStr">
@@ -37954,7 +37954,7 @@
       </c>
       <c r="H676" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="I676" t="inlineStr">
@@ -37974,7 +37974,7 @@
       </c>
       <c r="E677" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1,200,000</t>
         </is>
       </c>
       <c r="G677" t="inlineStr">
@@ -37985,8 +37985,8 @@
       </c>
       <c r="H677" t="inlineStr">
         <is>
-          <t>1
-200</t>
+          <t>1,000,000
+200,000</t>
         </is>
       </c>
       <c r="I677" t="inlineStr">
@@ -38006,7 +38006,7 @@
       </c>
       <c r="E678" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="G678" t="inlineStr">
@@ -38016,7 +38016,7 @@
       </c>
       <c r="H678" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="I678" t="inlineStr">
@@ -38038,9 +38038,9 @@
       </c>
       <c r="E679" t="inlineStr">
         <is>
-          <t>3
-1
-500</t>
+          <t>3,000,000
+1,500,000
+500,000</t>
         </is>
       </c>
       <c r="G679" t="inlineStr">
@@ -38050,7 +38050,7 @@
       </c>
       <c r="H679" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="I679" t="inlineStr">
@@ -38070,7 +38070,7 @@
       </c>
       <c r="E680" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>600,000</t>
         </is>
       </c>
       <c r="G680" t="inlineStr">
@@ -38081,8 +38081,8 @@
       </c>
       <c r="H680" t="inlineStr">
         <is>
-          <t>500
-100</t>
+          <t>500,000
+100,000</t>
         </is>
       </c>
       <c r="I680" t="inlineStr">
@@ -38102,7 +38102,7 @@
       </c>
       <c r="E681" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1,200,000</t>
         </is>
       </c>
       <c r="G681" t="inlineStr">
@@ -38113,8 +38113,8 @@
       </c>
       <c r="H681" t="inlineStr">
         <is>
-          <t>1
-200</t>
+          <t>1,000,000
+200,000</t>
         </is>
       </c>
       <c r="I681" t="inlineStr">
@@ -38134,7 +38134,7 @@
       </c>
       <c r="E682" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>600,000</t>
         </is>
       </c>
       <c r="G682" t="inlineStr">
@@ -38145,8 +38145,8 @@
       </c>
       <c r="H682" t="inlineStr">
         <is>
-          <t>500
-100</t>
+          <t>500,000
+100,000</t>
         </is>
       </c>
       <c r="I682" t="inlineStr">
@@ -38168,9 +38168,9 @@
       </c>
       <c r="E683" t="inlineStr">
         <is>
-          <t>3
-1
-500</t>
+          <t>3,000,000
+1,500,000
+500,000</t>
         </is>
       </c>
       <c r="G683" t="inlineStr">
@@ -38180,7 +38180,7 @@
       </c>
       <c r="H683" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="I683" t="inlineStr">
@@ -38200,7 +38200,7 @@
       </c>
       <c r="E684" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1,200,000</t>
         </is>
       </c>
       <c r="G684" t="inlineStr">
@@ -38211,8 +38211,8 @@
       </c>
       <c r="H684" t="inlineStr">
         <is>
-          <t>1
-200</t>
+          <t>1,000,000
+200,000</t>
         </is>
       </c>
       <c r="I684" t="inlineStr">
@@ -38234,9 +38234,9 @@
       </c>
       <c r="E685" t="inlineStr">
         <is>
-          <t>3
-1
-500</t>
+          <t>3,000,000
+1,500,000
+500,000</t>
         </is>
       </c>
       <c r="G685" t="inlineStr">
@@ -38246,7 +38246,7 @@
       </c>
       <c r="H685" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="I685" t="inlineStr">
@@ -38266,7 +38266,7 @@
       </c>
       <c r="E686" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1,200,000</t>
         </is>
       </c>
       <c r="G686" t="inlineStr">
@@ -38277,8 +38277,8 @@
       </c>
       <c r="H686" t="inlineStr">
         <is>
-          <t>1
-200</t>
+          <t>1,000,000
+200,000</t>
         </is>
       </c>
       <c r="I686" t="inlineStr">
@@ -38298,7 +38298,7 @@
       </c>
       <c r="E687" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1,200,000</t>
         </is>
       </c>
       <c r="G687" t="inlineStr">
@@ -38309,8 +38309,8 @@
       </c>
       <c r="H687" t="inlineStr">
         <is>
-          <t>1
-200</t>
+          <t>1,000,000
+200,000</t>
         </is>
       </c>
       <c r="I687" t="inlineStr">
@@ -38330,7 +38330,7 @@
       </c>
       <c r="E688" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="G688" t="inlineStr">
@@ -38340,7 +38340,7 @@
       </c>
       <c r="H688" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="I688" t="inlineStr">
@@ -38362,9 +38362,9 @@
       </c>
       <c r="E689" t="inlineStr">
         <is>
-          <t>3
-1
-500</t>
+          <t>3,000,000
+1,500,000
+500,000</t>
         </is>
       </c>
       <c r="G689" t="inlineStr">
@@ -38374,7 +38374,7 @@
       </c>
       <c r="H689" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="I689" t="inlineStr">
@@ -38394,7 +38394,7 @@
       </c>
       <c r="E690" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="G690" t="inlineStr">
@@ -38404,7 +38404,7 @@
       </c>
       <c r="H690" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="I690" t="inlineStr">
@@ -38424,7 +38424,7 @@
       </c>
       <c r="E691" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="G691" t="inlineStr">
@@ -38434,7 +38434,7 @@
       </c>
       <c r="H691" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="I691" t="inlineStr">
@@ -38454,7 +38454,7 @@
       </c>
       <c r="E692" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="G692" t="inlineStr">
@@ -38464,7 +38464,7 @@
       </c>
       <c r="H692" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="I692" t="inlineStr">
@@ -38484,7 +38484,7 @@
       </c>
       <c r="E693" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1,200,000</t>
         </is>
       </c>
       <c r="G693" t="inlineStr">
@@ -38495,8 +38495,8 @@
       </c>
       <c r="H693" t="inlineStr">
         <is>
-          <t>1
-200</t>
+          <t>1,000,000
+200,000</t>
         </is>
       </c>
       <c r="I693" t="inlineStr">
@@ -38516,7 +38516,7 @@
       </c>
       <c r="E694" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>600,000</t>
         </is>
       </c>
       <c r="G694" t="inlineStr">
@@ -38527,8 +38527,8 @@
       </c>
       <c r="H694" t="inlineStr">
         <is>
-          <t>500
-100</t>
+          <t>500,000
+100,000</t>
         </is>
       </c>
       <c r="I694" t="inlineStr">
@@ -38548,7 +38548,7 @@
       </c>
       <c r="E695" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="G695" t="inlineStr">
@@ -38558,7 +38558,7 @@
       </c>
       <c r="H695" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="I695" t="inlineStr">
@@ -38580,9 +38580,9 @@
       </c>
       <c r="E696" t="inlineStr">
         <is>
-          <t>3
-1
-500</t>
+          <t>3,000,000
+1,500,000
+500,000</t>
         </is>
       </c>
       <c r="G696" t="inlineStr">
@@ -38592,7 +38592,7 @@
       </c>
       <c r="H696" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="I696" t="inlineStr">
@@ -38612,7 +38612,7 @@
       </c>
       <c r="E697" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>600,000</t>
         </is>
       </c>
       <c r="G697" t="inlineStr">
@@ -38623,8 +38623,8 @@
       </c>
       <c r="H697" t="inlineStr">
         <is>
-          <t>500
-100</t>
+          <t>500,000
+100,000</t>
         </is>
       </c>
       <c r="I697" t="inlineStr">
@@ -38646,9 +38646,9 @@
       </c>
       <c r="E698" t="inlineStr">
         <is>
-          <t>3
-1
-500</t>
+          <t>3,000,000
+1,500,000
+500,000</t>
         </is>
       </c>
       <c r="G698" t="inlineStr">
@@ -38658,7 +38658,7 @@
       </c>
       <c r="H698" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="I698" t="inlineStr">
@@ -38678,7 +38678,7 @@
       </c>
       <c r="E699" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>600,000</t>
         </is>
       </c>
       <c r="G699" t="inlineStr">
@@ -38689,8 +38689,8 @@
       </c>
       <c r="H699" t="inlineStr">
         <is>
-          <t>500
-100</t>
+          <t>500,000
+100,000</t>
         </is>
       </c>
       <c r="I699" t="inlineStr">
@@ -38710,7 +38710,7 @@
       </c>
       <c r="E700" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="G700" t="inlineStr">
@@ -38720,7 +38720,7 @@
       </c>
       <c r="H700" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="I700" t="inlineStr">
@@ -38742,9 +38742,9 @@
       </c>
       <c r="E701" t="inlineStr">
         <is>
-          <t>3
-1
-500</t>
+          <t>3,000,000
+1,500,000
+500,000</t>
         </is>
       </c>
       <c r="G701" t="inlineStr">
@@ -38754,7 +38754,7 @@
       </c>
       <c r="H701" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="I701" t="inlineStr">
@@ -38776,9 +38776,9 @@
       </c>
       <c r="E702" t="inlineStr">
         <is>
-          <t>3
-1
-500</t>
+          <t>3,000,000
+1,500,000
+500,000</t>
         </is>
       </c>
       <c r="G702" t="inlineStr">
@@ -38788,7 +38788,7 @@
       </c>
       <c r="H702" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="I702" t="inlineStr">
@@ -38808,7 +38808,7 @@
       </c>
       <c r="E703" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>600,000</t>
         </is>
       </c>
       <c r="G703" t="inlineStr">
@@ -38819,8 +38819,8 @@
       </c>
       <c r="H703" t="inlineStr">
         <is>
-          <t>500
-100</t>
+          <t>500,000
+100,000</t>
         </is>
       </c>
       <c r="I703" t="inlineStr">
@@ -38840,7 +38840,7 @@
       </c>
       <c r="E704" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1,200,000</t>
         </is>
       </c>
       <c r="G704" t="inlineStr">
@@ -38851,8 +38851,8 @@
       </c>
       <c r="H704" t="inlineStr">
         <is>
-          <t>1
-200</t>
+          <t>1,000,000
+200,000</t>
         </is>
       </c>
       <c r="I704" t="inlineStr">
@@ -38872,7 +38872,7 @@
       </c>
       <c r="E705" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>600,000</t>
         </is>
       </c>
       <c r="G705" t="inlineStr">
@@ -38883,8 +38883,8 @@
       </c>
       <c r="H705" t="inlineStr">
         <is>
-          <t>500
-100</t>
+          <t>500,000
+100,000</t>
         </is>
       </c>
       <c r="I705" t="inlineStr">
@@ -38904,7 +38904,7 @@
       </c>
       <c r="E706" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1,200,000</t>
         </is>
       </c>
       <c r="G706" t="inlineStr">
@@ -38915,8 +38915,8 @@
       </c>
       <c r="H706" t="inlineStr">
         <is>
-          <t>1
-200</t>
+          <t>1,000,000
+200,000</t>
         </is>
       </c>
       <c r="I706" t="inlineStr">
@@ -38936,7 +38936,7 @@
       </c>
       <c r="E707" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="G707" t="inlineStr">
@@ -38946,7 +38946,7 @@
       </c>
       <c r="H707" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="I707" t="inlineStr">
@@ -38966,7 +38966,7 @@
       </c>
       <c r="E708" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1,200,000</t>
         </is>
       </c>
       <c r="G708" t="inlineStr">
@@ -38977,8 +38977,8 @@
       </c>
       <c r="H708" t="inlineStr">
         <is>
-          <t>1
-200</t>
+          <t>1,000,000
+200,000</t>
         </is>
       </c>
       <c r="I708" t="inlineStr">
@@ -38998,7 +38998,7 @@
       </c>
       <c r="E709" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="G709" t="inlineStr">
@@ -39008,7 +39008,7 @@
       </c>
       <c r="H709" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="I709" t="inlineStr">
@@ -39028,7 +39028,7 @@
       </c>
       <c r="E710" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>600,000</t>
         </is>
       </c>
       <c r="G710" t="inlineStr">
@@ -39039,8 +39039,8 @@
       </c>
       <c r="H710" t="inlineStr">
         <is>
-          <t>500
-100</t>
+          <t>500,000
+100,000</t>
         </is>
       </c>
       <c r="I710" t="inlineStr">
@@ -39062,9 +39062,9 @@
       </c>
       <c r="E711" t="inlineStr">
         <is>
-          <t>3
-1
-500</t>
+          <t>3,000,000
+1,500,000
+500,000</t>
         </is>
       </c>
       <c r="G711" t="inlineStr">
@@ -39074,7 +39074,7 @@
       </c>
       <c r="H711" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="I711" t="inlineStr">
@@ -39094,7 +39094,7 @@
       </c>
       <c r="E712" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>600,000</t>
         </is>
       </c>
       <c r="G712" t="inlineStr">
@@ -39105,8 +39105,8 @@
       </c>
       <c r="H712" t="inlineStr">
         <is>
-          <t>500
-100</t>
+          <t>500,000
+100,000</t>
         </is>
       </c>
       <c r="I712" t="inlineStr">
@@ -39126,7 +39126,7 @@
       </c>
       <c r="E713" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>600,000</t>
         </is>
       </c>
       <c r="G713" t="inlineStr">
@@ -39137,8 +39137,8 @@
       </c>
       <c r="H713" t="inlineStr">
         <is>
-          <t>500
-100</t>
+          <t>500,000
+100,000</t>
         </is>
       </c>
       <c r="I713" t="inlineStr">
@@ -39160,9 +39160,9 @@
       </c>
       <c r="E714" t="inlineStr">
         <is>
-          <t>3
-1
-500</t>
+          <t>3,000,000
+1,500,000
+500,000</t>
         </is>
       </c>
       <c r="G714" t="inlineStr">
@@ -39172,7 +39172,7 @@
       </c>
       <c r="H714" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="I714" t="inlineStr">
@@ -39192,7 +39192,7 @@
       </c>
       <c r="E715" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>600,000</t>
         </is>
       </c>
       <c r="G715" t="inlineStr">
@@ -39203,8 +39203,8 @@
       </c>
       <c r="H715" t="inlineStr">
         <is>
-          <t>500
-100</t>
+          <t>500,000
+100,000</t>
         </is>
       </c>
       <c r="I715" t="inlineStr">
@@ -39224,7 +39224,7 @@
       </c>
       <c r="E716" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="G716" t="inlineStr">
@@ -39234,7 +39234,7 @@
       </c>
       <c r="H716" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="I716" t="inlineStr">
@@ -39254,7 +39254,7 @@
       </c>
       <c r="E717" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="G717" t="inlineStr">
@@ -39264,7 +39264,7 @@
       </c>
       <c r="H717" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="I717" t="inlineStr">
@@ -39286,9 +39286,9 @@
       </c>
       <c r="E718" t="inlineStr">
         <is>
-          <t>3
-1
-500</t>
+          <t>3,000,000
+1,500,000
+500,000</t>
         </is>
       </c>
       <c r="G718" t="inlineStr">
@@ -39298,7 +39298,7 @@
       </c>
       <c r="H718" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="I718" t="inlineStr">
@@ -39318,7 +39318,7 @@
       </c>
       <c r="E719" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1,200,000</t>
         </is>
       </c>
       <c r="G719" t="inlineStr">
@@ -39329,8 +39329,8 @@
       </c>
       <c r="H719" t="inlineStr">
         <is>
-          <t>1
-200</t>
+          <t>1,000,000
+200,000</t>
         </is>
       </c>
       <c r="I719" t="inlineStr">
@@ -39350,7 +39350,7 @@
       </c>
       <c r="E720" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="G720" t="inlineStr">
@@ -39360,7 +39360,7 @@
       </c>
       <c r="H720" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="I720" t="inlineStr">
@@ -39382,9 +39382,9 @@
       </c>
       <c r="E721" t="inlineStr">
         <is>
-          <t>3
-1
-500</t>
+          <t>3,000,000
+1,500,000
+500,000</t>
         </is>
       </c>
       <c r="G721" t="inlineStr">
@@ -39394,7 +39394,7 @@
       </c>
       <c r="H721" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="I721" t="inlineStr">
@@ -39416,9 +39416,9 @@
       </c>
       <c r="E722" t="inlineStr">
         <is>
-          <t>3
-1
-500</t>
+          <t>3,000,000
+1,500,000
+500,000</t>
         </is>
       </c>
       <c r="G722" t="inlineStr">
@@ -39428,7 +39428,7 @@
       </c>
       <c r="H722" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="I722" t="inlineStr">
@@ -39448,7 +39448,7 @@
       </c>
       <c r="E723" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="G723" t="inlineStr">
@@ -39458,7 +39458,7 @@
       </c>
       <c r="H723" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="I723" t="inlineStr">
@@ -39478,7 +39478,7 @@
       </c>
       <c r="E724" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>600,000</t>
         </is>
       </c>
       <c r="G724" t="inlineStr">
@@ -39489,8 +39489,8 @@
       </c>
       <c r="H724" t="inlineStr">
         <is>
-          <t>500
-100</t>
+          <t>500,000
+100,000</t>
         </is>
       </c>
       <c r="I724" t="inlineStr">
@@ -39510,7 +39510,7 @@
       </c>
       <c r="E725" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>600,000</t>
         </is>
       </c>
       <c r="G725" t="inlineStr">
@@ -39521,8 +39521,8 @@
       </c>
       <c r="H725" t="inlineStr">
         <is>
-          <t>500
-100</t>
+          <t>500,000
+100,000</t>
         </is>
       </c>
       <c r="I725" t="inlineStr">
@@ -39542,7 +39542,7 @@
       </c>
       <c r="E726" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1,200,000</t>
         </is>
       </c>
       <c r="G726" t="inlineStr">
@@ -39553,8 +39553,8 @@
       </c>
       <c r="H726" t="inlineStr">
         <is>
-          <t>1
-200</t>
+          <t>1,000,000
+200,000</t>
         </is>
       </c>
       <c r="I726" t="inlineStr">
@@ -39574,7 +39574,7 @@
       </c>
       <c r="E727" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1,200,000</t>
         </is>
       </c>
       <c r="G727" t="inlineStr">
@@ -39585,8 +39585,8 @@
       </c>
       <c r="H727" t="inlineStr">
         <is>
-          <t>1
-200</t>
+          <t>1,000,000
+200,000</t>
         </is>
       </c>
       <c r="I727" t="inlineStr">
@@ -39606,7 +39606,7 @@
       </c>
       <c r="E728" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>600,000</t>
         </is>
       </c>
       <c r="G728" t="inlineStr">
@@ -39617,8 +39617,8 @@
       </c>
       <c r="H728" t="inlineStr">
         <is>
-          <t>500
-100</t>
+          <t>500,000
+100,000</t>
         </is>
       </c>
       <c r="I728" t="inlineStr">
@@ -39638,7 +39638,7 @@
       </c>
       <c r="E729" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="G729" t="inlineStr">
@@ -39648,7 +39648,7 @@
       </c>
       <c r="H729" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="I729" t="inlineStr">
@@ -39670,9 +39670,9 @@
       </c>
       <c r="E730" t="inlineStr">
         <is>
-          <t>3
-1
-500</t>
+          <t>3,000,000
+1,500,000
+500,000</t>
         </is>
       </c>
       <c r="G730" t="inlineStr">
@@ -39682,7 +39682,7 @@
       </c>
       <c r="H730" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="I730" t="inlineStr">
@@ -39702,7 +39702,7 @@
       </c>
       <c r="E731" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>600,000</t>
         </is>
       </c>
       <c r="G731" t="inlineStr">
@@ -39713,8 +39713,8 @@
       </c>
       <c r="H731" t="inlineStr">
         <is>
-          <t>500
-100</t>
+          <t>500,000
+100,000</t>
         </is>
       </c>
       <c r="I731" t="inlineStr">
@@ -39734,7 +39734,7 @@
       </c>
       <c r="E732" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1,200,000</t>
         </is>
       </c>
       <c r="G732" t="inlineStr">
@@ -39745,8 +39745,8 @@
       </c>
       <c r="H732" t="inlineStr">
         <is>
-          <t>1
-200</t>
+          <t>1,000,000
+200,000</t>
         </is>
       </c>
       <c r="I732" t="inlineStr">
@@ -39766,7 +39766,7 @@
       </c>
       <c r="E733" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1,200,000</t>
         </is>
       </c>
       <c r="G733" t="inlineStr">
@@ -39777,8 +39777,8 @@
       </c>
       <c r="H733" t="inlineStr">
         <is>
-          <t>1
-200</t>
+          <t>1,000,000
+200,000</t>
         </is>
       </c>
       <c r="I733" t="inlineStr">
@@ -39798,7 +39798,7 @@
       </c>
       <c r="E734" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1,200,000</t>
         </is>
       </c>
       <c r="G734" t="inlineStr">
@@ -39809,8 +39809,8 @@
       </c>
       <c r="H734" t="inlineStr">
         <is>
-          <t>1
-200</t>
+          <t>1,000,000
+200,000</t>
         </is>
       </c>
       <c r="I734" t="inlineStr">
@@ -39830,7 +39830,7 @@
       </c>
       <c r="E735" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1,200,000</t>
         </is>
       </c>
       <c r="G735" t="inlineStr">
@@ -39841,8 +39841,8 @@
       </c>
       <c r="H735" t="inlineStr">
         <is>
-          <t>1
-200</t>
+          <t>1,000,000
+200,000</t>
         </is>
       </c>
       <c r="I735" t="inlineStr">
@@ -39862,7 +39862,7 @@
       </c>
       <c r="E736" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="G736" t="inlineStr">
@@ -39872,7 +39872,7 @@
       </c>
       <c r="H736" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="I736" t="inlineStr">
@@ -39894,9 +39894,9 @@
       </c>
       <c r="E737" t="inlineStr">
         <is>
-          <t>3
-1
-500</t>
+          <t>3,000,000
+1,500,000
+500,000</t>
         </is>
       </c>
       <c r="G737" t="inlineStr">
@@ -39906,7 +39906,7 @@
       </c>
       <c r="H737" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="I737" t="inlineStr">
@@ -39928,9 +39928,9 @@
       </c>
       <c r="E738" t="inlineStr">
         <is>
-          <t>3
-1
-500</t>
+          <t>3,000,000
+1,500,000
+500,000</t>
         </is>
       </c>
       <c r="G738" t="inlineStr">
@@ -39940,7 +39940,7 @@
       </c>
       <c r="H738" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="I738" t="inlineStr">
@@ -39960,7 +39960,7 @@
       </c>
       <c r="E739" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>600,000</t>
         </is>
       </c>
       <c r="G739" t="inlineStr">
@@ -39971,8 +39971,8 @@
       </c>
       <c r="H739" t="inlineStr">
         <is>
-          <t>500
-100</t>
+          <t>500,000
+100,000</t>
         </is>
       </c>
       <c r="I739" t="inlineStr">
@@ -39994,9 +39994,9 @@
       </c>
       <c r="E740" t="inlineStr">
         <is>
-          <t>3
-1
-500</t>
+          <t>3,000,000
+1,500,000
+500,000</t>
         </is>
       </c>
       <c r="G740" t="inlineStr">
@@ -40006,7 +40006,7 @@
       </c>
       <c r="H740" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="I740" t="inlineStr">
@@ -40026,7 +40026,7 @@
       </c>
       <c r="E741" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1,200,000</t>
         </is>
       </c>
       <c r="G741" t="inlineStr">
@@ -40037,8 +40037,8 @@
       </c>
       <c r="H741" t="inlineStr">
         <is>
-          <t>1
-200</t>
+          <t>1,000,000
+200,000</t>
         </is>
       </c>
       <c r="I741" t="inlineStr">
